--- a/artfynd/S 1079-2025 artfynd.xlsx
+++ b/artfynd/S 1079-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89411</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89412</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89413</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97784</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/249161</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17277284</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,6 +1471,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17271452</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1546,6 +1586,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17277283</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1657,6 +1702,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/396649</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1767,6 +1817,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17277263</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1877,6 +1932,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17271429</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1987,6 +2047,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17271432</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2097,6 +2162,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17277287</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2207,6 +2277,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17271450</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2317,6 +2392,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17271454</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2427,6 +2507,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17277282</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2537,6 +2622,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17277285</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2638,6 +2728,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1829562</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2739,6 +2834,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1974071</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2840,6 +2940,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1893847</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2965,6 +3070,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1893849</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3066,6 +3176,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1893850</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3167,6 +3282,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1893851</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3278,6 +3398,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1893852</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3389,6 +3514,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1893853</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3500,6 +3630,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1893854</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3606,6 +3741,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1893859</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3717,6 +3857,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1893860</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3827,6 +3972,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17268990</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3937,6 +4087,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17269001</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4047,6 +4202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17277261</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4148,6 +4308,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2052395</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4258,6 +4423,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17277308</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4369,8 +4539,49 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6539513</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 1079-2025 artfynd.xlsx
+++ b/artfynd/S 1079-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ35"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4316,52 +4316,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>17277308</v>
+        <v>135979050</v>
       </c>
       <c r="B34" t="n">
-        <v>99118</v>
+        <v>6287</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>101520</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Större flatbagge</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Peltis grossa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vattensjön, Mpd</t>
+          <t>Sundsvallstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521215</v>
+        <v>521085</v>
       </c>
       <c r="R34" t="n">
-        <v>6937865</v>
+        <v>6937814</v>
       </c>
       <c r="S34" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4385,12 +4386,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2013-03-05</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2013-03-05</t>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Många kläckhål på bränd björklåga</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4401,78 +4407,73 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Löv/barrblandskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Joel Hallqvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Joel Hallqvist</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17277308</t>
+          <t>https://artportalen.se/Sighting/135979050</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6539513</v>
+        <v>17277308</v>
       </c>
       <c r="B35" t="n">
-        <v>80392</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stor-Gravberget, Mpd</t>
+          <t>Vattensjön, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>522017</v>
+        <v>521215</v>
       </c>
       <c r="R35" t="n">
-        <v>6937632</v>
+        <v>6937865</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4496,12 +4497,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2007-09-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2007-09-13</t>
+          <t>2013-03-05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4513,33 +4514,260 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>stavagranskog</t>
+          <t>Löv/barrblandskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17277308</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135977486</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sundsvallstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>521608</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6937655</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>I hyggeskant</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Hallqvist</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Hallqvist</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135977486</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>6539513</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stor-Gravberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>522017</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6937632</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2007-09-13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2007-09-13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>stavagranskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
           <t>Hans Sundström</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
+      <c r="AX37" t="inlineStr">
         <is>
           <t>Hans Sundström, * Naturskyddare</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr">
+      <c r="AY37" t="inlineStr">
         <is>
           <t>Naturskyddare</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
+      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6539513</t>
         </is>
@@ -4581,6 +4809,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1079-2025 artfynd.xlsx
+++ b/artfynd/S 1079-2025 artfynd.xlsx
@@ -4319,7 +4319,7 @@
         <v>135979050</v>
       </c>
       <c r="B34" t="n">
-        <v>6287</v>
+        <v>6289</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>135977486</v>
       </c>
       <c r="B36" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/S 1079-2025 artfynd.xlsx
+++ b/artfynd/S 1079-2025 artfynd.xlsx
@@ -4546,7 +4546,7 @@
         <v>135977486</v>
       </c>
       <c r="B36" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/S 1079-2025 artfynd.xlsx
+++ b/artfynd/S 1079-2025 artfynd.xlsx
@@ -4546,7 +4546,7 @@
         <v>135977486</v>
       </c>
       <c r="B36" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/S 1079-2025 artfynd.xlsx
+++ b/artfynd/S 1079-2025 artfynd.xlsx
@@ -4546,7 +4546,7 @@
         <v>135977486</v>
       </c>
       <c r="B36" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/S 1079-2025 artfynd.xlsx
+++ b/artfynd/S 1079-2025 artfynd.xlsx
@@ -4546,7 +4546,7 @@
         <v>135977486</v>
       </c>
       <c r="B36" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/S 1079-2025 artfynd.xlsx
+++ b/artfynd/S 1079-2025 artfynd.xlsx
@@ -4546,7 +4546,7 @@
         <v>135977486</v>
       </c>
       <c r="B36" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/S 1079-2025 artfynd.xlsx
+++ b/artfynd/S 1079-2025 artfynd.xlsx
@@ -4546,7 +4546,7 @@
         <v>135977486</v>
       </c>
       <c r="B36" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/S 1079-2025 artfynd.xlsx
+++ b/artfynd/S 1079-2025 artfynd.xlsx
@@ -4546,7 +4546,7 @@
         <v>135977486</v>
       </c>
       <c r="B36" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/S 1079-2025 artfynd.xlsx
+++ b/artfynd/S 1079-2025 artfynd.xlsx
@@ -4546,7 +4546,7 @@
         <v>135977486</v>
       </c>
       <c r="B36" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/S 1079-2025 artfynd.xlsx
+++ b/artfynd/S 1079-2025 artfynd.xlsx
@@ -4546,7 +4546,7 @@
         <v>135977486</v>
       </c>
       <c r="B36" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/S 1079-2025 artfynd.xlsx
+++ b/artfynd/S 1079-2025 artfynd.xlsx
@@ -4546,7 +4546,7 @@
         <v>135977486</v>
       </c>
       <c r="B36" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
